--- a/outputs/daily/hr_rankings_2026-08-12.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-12.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>56.3</v>
       </c>
       <c r="R2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2135,22 +2135,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>672284</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jarred Kelenic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2160,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>80</v>
       </c>
-      <c r="Q7" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>50</v>
-      </c>
       <c r="U7" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2252,7 +2252,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2269,127 +2269,127 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>104.3548</t>
+          <t>102.1024</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5909</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.47</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.0959</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -2415,22 +2415,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>672284</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jarred Kelenic</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2440,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>64.8</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.7</v>
+        <v>25.7</v>
       </c>
       <c r="R8" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2549,127 +2549,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/8, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.1024</t>
+          <t>104.3548</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.5909</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>47.19</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0959</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>56.3</v>
       </c>
       <c r="R10" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>56.3</v>
       </c>
       <c r="R11" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>56.3</v>
       </c>
       <c r="R13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>25.7</v>
       </c>
       <c r="R16" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>25.7</v>
       </c>
       <c r="R17" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>56.3</v>
       </c>
       <c r="R19" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>25.7</v>
       </c>
       <c r="R20" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S20" t="n">
         <v>96.59999999999999</v>
@@ -6055,22 +6055,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6080,31 +6080,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6118,26 +6118,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>25.7</v>
+        <v>48.5</v>
       </c>
       <c r="R21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S21" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>52.3</v>
+        <v>34.4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6219,97 +6219,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.4859</t>
+          <t>97.0675</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6360,31 +6360,31 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6398,26 +6398,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>13.7</v>
+        <v>32.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.5</v>
+        <v>25.7</v>
       </c>
       <c r="R22" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S22" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>34.4</v>
+        <v>52.3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6499,97 +6499,97 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>37.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>97.0675</t>
+          <t>98.4859</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.3859</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3293</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>25.7</v>
       </c>
       <c r="R23" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S23" t="n">
         <v>94.90000000000001</v>
@@ -6895,22 +6895,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6920,27 +6920,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -6958,26 +6958,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>54.2</v>
+        <v>48.5</v>
       </c>
       <c r="R24" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S24" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T24" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>30</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7012,7 +7012,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7044,112 +7044,112 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>99.9587</t>
+          <t>96.1524</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3387</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3094</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7175,12 +7175,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7238,11 +7238,11 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>10.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q25" t="n">
         <v>48.5</v>
@@ -7251,13 +7251,13 @@
         <v>65.2</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T25" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7339,67 +7339,67 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>96.1524</t>
+          <t>99.4792</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7480,31 +7480,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,26 +7518,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>28.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48.5</v>
+        <v>54.2</v>
       </c>
       <c r="R26" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S26" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U26" t="n">
-        <v>9.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7572,7 +7572,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7604,112 +7604,112 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>99.4792</t>
+          <t>99.9587</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3387</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3094</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>25.7</v>
       </c>
       <c r="R28" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S28" t="n">
         <v>64.3</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8575,22 +8575,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>686475</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tyler Tolbert</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8610,21 +8610,21 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8638,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>56.3</v>
+        <v>45.7</v>
       </c>
       <c r="R30" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,112 +8724,112 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>97.085</t>
+          <t>99.4614</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3417</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.0823</t>
+          <t>0.1243</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.2596</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>69.39</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>38.98</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1413</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8855,24 +8855,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>672724</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>2026-08-13T02:10:00Z</t>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>45.7</v>
+        <v>48.5</v>
       </c>
       <c r="R31" t="n">
         <v>65.2</v>
@@ -8937,7 +8937,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9019,97 +9019,97 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>99.4614</t>
+          <t>99.9234</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.3417</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1243</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.2596</t>
+          <t>0.2641</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1126</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
@@ -9135,22 +9135,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>672724</t>
+          <t>686475</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Tyler Tolbert</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9170,21 +9170,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>23.5</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>48.5</v>
+        <v>56.3</v>
       </c>
       <c r="R32" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S32" t="n">
         <v>52.4</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,112 +9284,112 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.9234</t>
+          <t>97.085</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.0823</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2641</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>69.39</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1126</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>25.7</v>
       </c>
       <c r="R34" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>56.3</v>
       </c>
       <c r="R35" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S35" t="n">
         <v>44.8</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>25.7</v>
       </c>
       <c r="R36" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S36" t="n">
         <v>44.8</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>56.3</v>
       </c>
       <c r="R2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12541,22 +12541,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>672284</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jarred Kelenic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12566,31 +12566,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12604,26 +12604,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>80</v>
       </c>
-      <c r="Q7" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>50</v>
-      </c>
       <c r="U7" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -12658,7 +12658,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -12675,127 +12675,127 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>104.3548</t>
+          <t>102.1024</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5909</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.47</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.0959</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -12821,22 +12821,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>672284</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jarred Kelenic</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -12846,31 +12846,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12884,26 +12884,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>64.8</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.7</v>
+        <v>25.7</v>
       </c>
       <c r="R8" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -12938,7 +12938,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -12955,127 +12955,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/8, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.1024</t>
+          <t>104.3548</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.5909</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>47.19</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0959</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>56.3</v>
       </c>
       <c r="R10" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>56.3</v>
       </c>
       <c r="R11" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>56.3</v>
       </c>
       <c r="R13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>25.7</v>
       </c>
       <c r="R16" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>25.7</v>
       </c>
       <c r="R17" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>56.3</v>
       </c>
       <c r="R19" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>25.7</v>
       </c>
       <c r="R20" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S20" t="n">
         <v>96.59999999999999</v>
@@ -16461,22 +16461,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -16486,31 +16486,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16524,26 +16524,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>25.7</v>
+        <v>48.5</v>
       </c>
       <c r="R21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S21" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>52.3</v>
+        <v>34.4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -16595,12 +16595,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16610,12 +16610,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16625,97 +16625,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.4859</t>
+          <t>97.0675</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -16725,12 +16725,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
